--- a/input_parameters_shiny.xlsx
+++ b/input_parameters_shiny.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pauld\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pauld\Documents\Climate Impact Onions Forecast\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C0B4E39A-3BD0-4382-B12E-3F276D50912A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B34544A6-1801-4D69-BB99-0ABC198A65FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="815" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" tabRatio="815" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet_names" sheetId="2" r:id="rId1"/>
@@ -127,15 +127,9 @@
     <t>LAI_maturation_p</t>
   </si>
   <si>
-    <t>HI_onions_p</t>
-  </si>
-  <si>
     <t>onions_per_ha_p</t>
   </si>
   <si>
-    <t>dry_onion_weight_p</t>
-  </si>
-  <si>
     <t>g/MJ</t>
   </si>
   <si>
@@ -214,9 +208,6 @@
     <t>impact_days_hail_t</t>
   </si>
   <si>
-    <t>yield_reduction_hail_p</t>
-  </si>
-  <si>
     <t>impact_days_wet_botrytis_t</t>
   </si>
   <si>
@@ -349,15 +340,9 @@
     <t xml:space="preserve">Temperaturbereich in dem ein hohes Risiko für einen Zwiebelhalsfäule Befall vorliegt. </t>
   </si>
   <si>
-    <t>prec_drought_threshold_p</t>
-  </si>
-  <si>
     <t>Tavg_drought_threshold_p</t>
   </si>
   <si>
-    <t>impact_prec_drought_t</t>
-  </si>
-  <si>
     <t>impact_days_dry_drought_t</t>
   </si>
   <si>
@@ -791,6 +776,21 @@
   </si>
   <si>
     <t>Mindestanzahl trockener Tage ohne Niederschlag, die vor der Aussaat erforderlich sind, um eine gute Bodenstruktur sicherzustellen.</t>
+  </si>
+  <si>
+    <t>HI_onions_t</t>
+  </si>
+  <si>
+    <t>dry_onion_weight_t</t>
+  </si>
+  <si>
+    <t>yield_reduction_hail_t</t>
+  </si>
+  <si>
+    <t>rh_drought_threshold_p</t>
+  </si>
+  <si>
+    <t>impact_rh_drought_t</t>
   </si>
 </sst>
 </file>
@@ -857,7 +857,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -880,8 +880,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1210,31 +1208,31 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B6" t="s">
         <v>10</v>
@@ -1302,10 +1300,10 @@
         <v>4</v>
       </c>
       <c r="F2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="H2" t="s">
         <v>14</v>
@@ -1328,10 +1326,10 @@
         <v>4</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>14</v>
@@ -1340,7 +1338,7 @@
         <v>100</v>
       </c>
       <c r="J3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1355,7 +1353,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{546B24F0-A477-4B95-8562-CC4F97744405}">
-  <dimension ref="A1:O28"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.5703125" style="2" bestFit="1" customWidth="1"/>
@@ -1364,7 +1362,7 @@
     <col min="7" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1396,9 +1394,9 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>246</v>
       </c>
       <c r="B2">
         <v>0.65</v>
@@ -1407,14 +1405,14 @@
         <v>0.85</v>
       </c>
       <c r="D2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E2"/>
       <c r="F2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="G2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H2" t="s">
         <v>14</v>
@@ -1423,13 +1421,13 @@
         <v>0.1</v>
       </c>
       <c r="J2" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="K2"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B3">
         <v>700000</v>
@@ -1441,13 +1439,13 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H3" t="s">
         <v>14</v>
@@ -1456,13 +1454,13 @@
         <v>0.1</v>
       </c>
       <c r="J3" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="K3"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>247</v>
       </c>
       <c r="B4">
         <v>0.88</v>
@@ -1471,14 +1469,14 @@
         <v>0.92</v>
       </c>
       <c r="D4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E4"/>
       <c r="F4" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G4" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H4" t="s">
         <v>14</v>
@@ -1487,423 +1485,343 @@
         <v>0.05</v>
       </c>
       <c r="J4" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="K4"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>221</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+      <c r="D5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" t="s">
+        <v>222</v>
+      </c>
+      <c r="G5" t="s">
+        <v>223</v>
+      </c>
+      <c r="H5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5">
+        <v>0.5</v>
+      </c>
+      <c r="J5" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>225</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" t="s">
         <v>226</v>
       </c>
-      <c r="B5" s="11">
+      <c r="F6" t="s">
+        <v>227</v>
+      </c>
+      <c r="G6" t="s">
+        <v>228</v>
+      </c>
+      <c r="H6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>229</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7">
         <v>4</v>
       </c>
-      <c r="C5" s="11">
+      <c r="D7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" t="s">
+        <v>226</v>
+      </c>
+      <c r="F7" t="s">
+        <v>230</v>
+      </c>
+      <c r="G7" t="s">
+        <v>231</v>
+      </c>
+      <c r="H7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>239</v>
+      </c>
+      <c r="B8">
         <v>6</v>
       </c>
-      <c r="D5" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>227</v>
-      </c>
-      <c r="G5" s="11" t="s">
-        <v>228</v>
-      </c>
-      <c r="H5" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="J5" s="11" t="s">
-        <v>229</v>
-      </c>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
-      <c r="N5" s="10"/>
-      <c r="O5" s="10"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
-        <v>230</v>
-      </c>
-      <c r="B6" s="11">
-        <v>2</v>
-      </c>
-      <c r="C6" s="11">
+      <c r="C8">
+        <v>10</v>
+      </c>
+      <c r="D8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" t="s">
+        <v>240</v>
+      </c>
+      <c r="F8" t="s">
+        <v>241</v>
+      </c>
+      <c r="G8" t="s">
+        <v>242</v>
+      </c>
+      <c r="H8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>243</v>
+      </c>
+      <c r="B9">
+        <v>3</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+      <c r="D9" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="F6" s="11" t="s">
+      <c r="E9" t="s">
+        <v>226</v>
+      </c>
+      <c r="F9" t="s">
+        <v>244</v>
+      </c>
+      <c r="G9" t="s">
+        <v>245</v>
+      </c>
+      <c r="H9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>232</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="B10">
+        <v>45</v>
+      </c>
+      <c r="C10">
+        <v>45</v>
+      </c>
+      <c r="D10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" t="s">
         <v>233</v>
       </c>
-      <c r="H6" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" s="11">
+      <c r="F10" t="s">
+        <v>234</v>
+      </c>
+      <c r="G10" t="s">
+        <v>235</v>
+      </c>
+      <c r="H10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I10">
         <v>1</v>
       </c>
-      <c r="J6" s="11" t="s">
-        <v>229</v>
-      </c>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10"/>
-      <c r="N6" s="10"/>
-      <c r="O6" s="10"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
-        <v>234</v>
-      </c>
-      <c r="B7" s="11">
-        <v>2</v>
-      </c>
-      <c r="C7" s="11">
+      <c r="J10" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>236</v>
+      </c>
+      <c r="B11">
+        <v>100</v>
+      </c>
+      <c r="C11">
+        <v>100</v>
+      </c>
+      <c r="D11" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>235</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>236</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="I7" s="11">
+      <c r="E11" t="s">
+        <v>233</v>
+      </c>
+      <c r="F11" t="s">
+        <v>237</v>
+      </c>
+      <c r="G11" t="s">
+        <v>238</v>
+      </c>
+      <c r="H11" t="s">
+        <v>14</v>
+      </c>
+      <c r="I11">
         <v>1</v>
       </c>
-      <c r="J7" s="11" t="s">
-        <v>229</v>
-      </c>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
-      <c r="N7" s="10"/>
-      <c r="O7" s="10"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
-        <v>244</v>
-      </c>
-      <c r="B8" s="11">
-        <v>6</v>
-      </c>
-      <c r="C8" s="11">
-        <v>10</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>245</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>246</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="H8" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="I8" s="11">
-        <v>1</v>
-      </c>
-      <c r="J8" s="11" t="s">
-        <v>229</v>
-      </c>
-      <c r="K8" s="10"/>
-      <c r="L8" s="10"/>
-      <c r="M8" s="10"/>
-      <c r="N8" s="10"/>
-      <c r="O8" s="10"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
-        <v>248</v>
-      </c>
-      <c r="B9" s="11">
-        <v>3</v>
-      </c>
-      <c r="C9" s="11">
-        <v>3</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>249</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>250</v>
-      </c>
-      <c r="H9" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="I9" s="11">
-        <v>1</v>
-      </c>
-      <c r="J9" s="11" t="s">
-        <v>229</v>
-      </c>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10"/>
-      <c r="M9" s="10"/>
-      <c r="N9" s="10"/>
-      <c r="O9" s="10"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="s">
-        <v>237</v>
-      </c>
-      <c r="B10" s="11">
-        <v>45</v>
-      </c>
-      <c r="C10" s="11">
-        <v>45</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>238</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="I10" s="11">
-        <v>1</v>
-      </c>
-      <c r="J10" s="11" t="s">
-        <v>229</v>
-      </c>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="10"/>
-      <c r="N10" s="10"/>
-      <c r="O10" s="10"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="s">
-        <v>241</v>
-      </c>
-      <c r="B11" s="11">
-        <v>100</v>
-      </c>
-      <c r="C11" s="11">
-        <v>100</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>238</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>243</v>
-      </c>
-      <c r="H11" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="I11" s="11">
-        <v>1</v>
-      </c>
-      <c r="J11" s="11" t="s">
-        <v>229</v>
-      </c>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="10"/>
-      <c r="N11" s="10"/>
-      <c r="O11" s="10"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10"/>
-      <c r="M12" s="10"/>
-      <c r="N12" s="10"/>
-      <c r="O12" s="10"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10"/>
-      <c r="M13" s="10"/>
-      <c r="N13" s="10"/>
-      <c r="O13" s="10"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="11"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10"/>
-      <c r="M14" s="10"/>
-      <c r="N14" s="10"/>
-      <c r="O14" s="10"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="11"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
-      <c r="N15" s="10"/>
-      <c r="O15" s="10"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="11"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="10"/>
-      <c r="L16" s="10"/>
-      <c r="M16" s="10"/>
-      <c r="N16" s="10"/>
-      <c r="O16" s="10"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="11"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="11"/>
-      <c r="K17" s="10"/>
-      <c r="L17" s="10"/>
-      <c r="M17" s="10"/>
-      <c r="N17" s="10"/>
-      <c r="O17" s="10"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="11"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="11"/>
-      <c r="J18" s="11"/>
-      <c r="K18" s="10"/>
-      <c r="L18" s="10"/>
-      <c r="M18" s="10"/>
-      <c r="N18" s="10"/>
-      <c r="O18" s="10"/>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="12"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="12"/>
-      <c r="K19" s="10"/>
-      <c r="L19" s="10"/>
-      <c r="M19" s="10"/>
-      <c r="N19" s="10"/>
-      <c r="O19" s="10"/>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="J11" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12"/>
+      <c r="B12"/>
+      <c r="C12"/>
+      <c r="D12"/>
+      <c r="E12"/>
+      <c r="F12"/>
+      <c r="G12"/>
+      <c r="H12"/>
+      <c r="I12"/>
+      <c r="J12"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13"/>
+      <c r="B13"/>
+      <c r="C13"/>
+      <c r="D13"/>
+      <c r="E13"/>
+      <c r="F13"/>
+      <c r="G13"/>
+      <c r="H13"/>
+      <c r="I13"/>
+      <c r="J13"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14"/>
+      <c r="B14"/>
+      <c r="C14"/>
+      <c r="D14"/>
+      <c r="E14"/>
+      <c r="F14"/>
+      <c r="G14"/>
+      <c r="H14"/>
+      <c r="I14"/>
+      <c r="J14"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15"/>
+      <c r="B15"/>
+      <c r="C15"/>
+      <c r="D15"/>
+      <c r="E15"/>
+      <c r="F15"/>
+      <c r="G15"/>
+      <c r="H15"/>
+      <c r="I15"/>
+      <c r="J15"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16"/>
+      <c r="B16"/>
+      <c r="C16"/>
+      <c r="D16"/>
+      <c r="E16"/>
+      <c r="F16"/>
+      <c r="G16"/>
+      <c r="H16"/>
+      <c r="I16"/>
+      <c r="J16"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17"/>
+      <c r="B17"/>
+      <c r="C17"/>
+      <c r="D17"/>
+      <c r="E17"/>
+      <c r="F17"/>
+      <c r="G17"/>
+      <c r="H17"/>
+      <c r="I17"/>
+      <c r="J17"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18"/>
+      <c r="B18"/>
+      <c r="C18"/>
+      <c r="D18"/>
+      <c r="E18"/>
+      <c r="F18"/>
+      <c r="G18"/>
+      <c r="H18"/>
+      <c r="I18"/>
+      <c r="J18"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="10"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="10"/>
+      <c r="J19" s="10"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="8"/>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
-      <c r="F20" s="13"/>
+      <c r="F20" s="11"/>
       <c r="G20" s="8"/>
       <c r="H20" s="8"/>
       <c r="I20" s="8"/>
       <c r="J20" s="8"/>
-      <c r="K20" s="10"/>
-      <c r="L20" s="10"/>
-      <c r="M20" s="10"/>
-      <c r="N20" s="10"/>
-      <c r="O20" s="10"/>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="8"/>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
@@ -1914,13 +1832,8 @@
       <c r="H21" s="8"/>
       <c r="I21" s="8"/>
       <c r="J21" s="8"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="10"/>
-      <c r="M21" s="10"/>
-      <c r="N21" s="10"/>
-      <c r="O21" s="10"/>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="8"/>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
@@ -1931,13 +1844,8 @@
       <c r="H22" s="8"/>
       <c r="I22" s="8"/>
       <c r="J22" s="8"/>
-      <c r="K22" s="10"/>
-      <c r="L22" s="10"/>
-      <c r="M22" s="10"/>
-      <c r="N22" s="10"/>
-      <c r="O22" s="10"/>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="9"/>
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
@@ -1949,7 +1857,7 @@
       <c r="I23" s="9"/>
       <c r="J23" s="9"/>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="9"/>
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
@@ -1961,7 +1869,7 @@
       <c r="I24" s="9"/>
       <c r="J24" s="9"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="9"/>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
@@ -1973,7 +1881,7 @@
       <c r="I25" s="9"/>
       <c r="J25" s="9"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="9"/>
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
@@ -1985,7 +1893,7 @@
       <c r="I26" s="9"/>
       <c r="J26" s="9"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="9"/>
       <c r="B27" s="9"/>
       <c r="C27" s="9"/>
@@ -1997,7 +1905,7 @@
       <c r="I27" s="9"/>
       <c r="J27" s="9"/>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="9"/>
       <c r="B28" s="9"/>
       <c r="C28" s="9"/>
@@ -2018,7 +1926,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95267B7B-4544-45E1-AE00-31F080BD66E3}">
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="48.28515625" style="2" bestFit="1" customWidth="1"/>
@@ -2065,15 +1973,15 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F2" s="4" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B3">
         <v>25</v>
@@ -2085,13 +1993,13 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="H3" t="s">
         <v>14</v>
@@ -2100,7 +2008,7 @@
         <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K3"/>
       <c r="L3"/>
@@ -2108,7 +2016,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B4">
         <v>45</v>
@@ -2120,13 +2028,13 @@
         <v>5</v>
       </c>
       <c r="E4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="H4" t="s">
         <v>14</v>
@@ -2135,7 +2043,7 @@
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K4"/>
       <c r="L4"/>
@@ -2143,7 +2051,7 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B5">
         <v>0.3</v>
@@ -2152,14 +2060,14 @@
         <v>0.8</v>
       </c>
       <c r="D5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E5"/>
       <c r="F5" s="8" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="H5" t="s">
         <v>14</v>
@@ -2168,7 +2076,7 @@
         <v>0.1</v>
       </c>
       <c r="J5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K5"/>
       <c r="L5"/>
@@ -2176,7 +2084,7 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B6">
         <v>0.6</v>
@@ -2185,14 +2093,14 @@
         <v>0.85</v>
       </c>
       <c r="D6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E6"/>
       <c r="F6" s="8" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="H6" t="s">
         <v>14</v>
@@ -2201,7 +2109,7 @@
         <v>0.05</v>
       </c>
       <c r="J6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K6"/>
       <c r="L6"/>
@@ -2209,12 +2117,12 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F8" s="4" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B9">
         <v>20</v>
@@ -2226,13 +2134,13 @@
         <v>5</v>
       </c>
       <c r="E9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="H9" t="s">
         <v>14</v>
@@ -2241,7 +2149,7 @@
         <v>1</v>
       </c>
       <c r="J9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K9"/>
       <c r="L9"/>
@@ -2250,7 +2158,7 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B10">
         <v>18</v>
@@ -2262,13 +2170,13 @@
         <v>5</v>
       </c>
       <c r="E10" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="H10" t="s">
         <v>14</v>
@@ -2277,7 +2185,7 @@
         <v>1</v>
       </c>
       <c r="J10" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K10"/>
       <c r="L10"/>
@@ -2286,7 +2194,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B11">
         <v>0.3</v>
@@ -2295,14 +2203,14 @@
         <v>0.8</v>
       </c>
       <c r="D11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E11"/>
       <c r="F11" s="8" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="H11" t="s">
         <v>14</v>
@@ -2311,7 +2219,7 @@
         <v>0.1</v>
       </c>
       <c r="J11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K11"/>
       <c r="L11"/>
@@ -2320,7 +2228,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>58</v>
+        <v>248</v>
       </c>
       <c r="B12">
         <v>0.5</v>
@@ -2329,14 +2237,14 @@
         <v>0.8</v>
       </c>
       <c r="D12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E12"/>
       <c r="F12" s="8" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="H12" t="s">
         <v>14</v>
@@ -2345,7 +2253,7 @@
         <v>0.05</v>
       </c>
       <c r="J12" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K12"/>
       <c r="L12"/>
@@ -2354,30 +2262,30 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F14" s="6" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>103</v>
+        <v>249</v>
       </c>
       <c r="B15">
-        <v>4</v>
+        <v>85</v>
       </c>
       <c r="C15">
-        <v>6</v>
+        <v>90</v>
       </c>
       <c r="D15" t="s">
         <v>5</v>
       </c>
       <c r="E15" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="H15" t="s">
         <v>14</v>
@@ -2386,12 +2294,12 @@
         <v>1</v>
       </c>
       <c r="J15" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B16">
         <v>24</v>
@@ -2403,13 +2311,13 @@
         <v>5</v>
       </c>
       <c r="E16" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="H16" t="s">
         <v>14</v>
@@ -2418,12 +2326,12 @@
         <v>1</v>
       </c>
       <c r="J16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>105</v>
+        <v>250</v>
       </c>
       <c r="B17">
         <v>0.5</v>
@@ -2432,14 +2340,14 @@
         <v>0.6</v>
       </c>
       <c r="D17" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E17"/>
       <c r="F17" s="8" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="H17" t="s">
         <v>14</v>
@@ -2448,12 +2356,12 @@
         <v>0.1</v>
       </c>
       <c r="J17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B18">
         <v>0.6</v>
@@ -2462,14 +2370,14 @@
         <v>0.7</v>
       </c>
       <c r="D18" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E18"/>
       <c r="F18" s="8" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="H18" t="s">
         <v>14</v>
@@ -2478,12 +2386,12 @@
         <v>0.05</v>
       </c>
       <c r="J18" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B19">
         <v>0.2</v>
@@ -2492,16 +2400,16 @@
         <v>0.3</v>
       </c>
       <c r="D19" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E19" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="H19" t="s">
         <v>14</v>
@@ -2510,12 +2418,12 @@
         <v>0.5</v>
       </c>
       <c r="J19" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B20">
         <v>0.6</v>
@@ -2524,14 +2432,14 @@
         <v>0.9</v>
       </c>
       <c r="D20" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E20"/>
       <c r="F20" s="8" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="H20" t="s">
         <v>14</v>
@@ -2540,8 +2448,26 @@
         <v>0.05</v>
       </c>
       <c r="J20" t="s">
-        <v>51</v>
-      </c>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2599,15 +2525,15 @@
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="F2" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="B3">
         <v>85</v>
@@ -2619,13 +2545,13 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F3" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G3" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="H3" t="s">
         <v>14</v>
@@ -2634,12 +2560,12 @@
         <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B4">
         <v>15</v>
@@ -2651,13 +2577,13 @@
         <v>5</v>
       </c>
       <c r="E4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F4" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="G4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H4" t="s">
         <v>14</v>
@@ -2666,12 +2592,12 @@
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="B5">
         <v>3</v>
@@ -2683,13 +2609,13 @@
         <v>5</v>
       </c>
       <c r="E5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F5" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="G5" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="H5" t="s">
         <v>14</v>
@@ -2698,12 +2624,12 @@
         <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="B6">
         <v>0.4</v>
@@ -2712,14 +2638,14 @@
         <v>0.6</v>
       </c>
       <c r="D6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E6"/>
       <c r="F6" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="G6" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="H6" t="s">
         <v>14</v>
@@ -2728,12 +2654,12 @@
         <v>0.1</v>
       </c>
       <c r="J6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B7">
         <v>0.5</v>
@@ -2742,14 +2668,14 @@
         <v>0.7</v>
       </c>
       <c r="D7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E7"/>
       <c r="F7" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="G7" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="H7" t="s">
         <v>14</v>
@@ -2758,12 +2684,12 @@
         <v>0.1</v>
       </c>
       <c r="J7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B8">
         <v>0.6</v>
@@ -2772,14 +2698,14 @@
         <v>0.8</v>
       </c>
       <c r="D8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E8"/>
       <c r="F8" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="G8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H8" t="s">
         <v>14</v>
@@ -2788,7 +2714,7 @@
         <v>0.05</v>
       </c>
       <c r="J8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -2796,13 +2722,13 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F10" s="5" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J10"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B11">
         <v>85</v>
@@ -2814,13 +2740,13 @@
         <v>5</v>
       </c>
       <c r="E11" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F11" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="G11" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="H11" t="s">
         <v>14</v>
@@ -2829,12 +2755,12 @@
         <v>1</v>
       </c>
       <c r="J11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B12">
         <v>16</v>
@@ -2846,13 +2772,13 @@
         <v>5</v>
       </c>
       <c r="E12" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F12" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="G12" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="H12" t="s">
         <v>14</v>
@@ -2861,12 +2787,12 @@
         <v>1</v>
       </c>
       <c r="J12" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B13">
         <v>3</v>
@@ -2878,13 +2804,13 @@
         <v>5</v>
       </c>
       <c r="E13" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="G13" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="H13" t="s">
         <v>14</v>
@@ -2893,12 +2819,12 @@
         <v>1</v>
       </c>
       <c r="J13" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="B14">
         <v>0.4</v>
@@ -2907,16 +2833,16 @@
         <v>0.6</v>
       </c>
       <c r="D14" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E14" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F14" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="G14" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="H14" t="s">
         <v>14</v>
@@ -2925,12 +2851,12 @@
         <v>0.1</v>
       </c>
       <c r="J14" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B15">
         <v>0.3</v>
@@ -2939,14 +2865,14 @@
         <v>0.5</v>
       </c>
       <c r="D15" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E15"/>
       <c r="F15" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="G15" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="H15" t="s">
         <v>14</v>
@@ -2955,12 +2881,12 @@
         <v>0.1</v>
       </c>
       <c r="J15" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B16">
         <v>0.6</v>
@@ -2973,10 +2899,10 @@
       </c>
       <c r="E16"/>
       <c r="F16" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="G16" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H16" t="s">
         <v>14</v>
@@ -2985,7 +2911,7 @@
         <v>0.05</v>
       </c>
       <c r="J16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
@@ -2993,13 +2919,13 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F18" s="6" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="J18"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -3011,13 +2937,13 @@
         <v>5</v>
       </c>
       <c r="E19" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F19" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="H19" t="s">
         <v>14</v>
@@ -3026,12 +2952,12 @@
         <v>1</v>
       </c>
       <c r="J19" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="B20">
         <v>22</v>
@@ -3043,13 +2969,13 @@
         <v>5</v>
       </c>
       <c r="E20" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="H20" t="s">
         <v>14</v>
@@ -3058,7 +2984,7 @@
         <v>1</v>
       </c>
       <c r="J20" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K20"/>
       <c r="L20"/>
@@ -3067,7 +2993,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="B21">
         <v>4</v>
@@ -3079,13 +3005,13 @@
         <v>5</v>
       </c>
       <c r="E21" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="H21" t="s">
         <v>14</v>
@@ -3094,7 +3020,7 @@
         <v>1</v>
       </c>
       <c r="J21" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K21"/>
       <c r="L21"/>
@@ -3103,7 +3029,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="B22">
         <v>0.3</v>
@@ -3112,16 +3038,16 @@
         <v>0.7</v>
       </c>
       <c r="D22" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E22" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="H22" t="s">
         <v>14</v>
@@ -3130,12 +3056,12 @@
         <v>0.1</v>
       </c>
       <c r="J22" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B23">
         <v>0.2</v>
@@ -3144,14 +3070,14 @@
         <v>0.6</v>
       </c>
       <c r="D23" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E23"/>
       <c r="F23" s="8" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="H23" t="s">
         <v>14</v>
@@ -3160,7 +3086,7 @@
         <v>0.1</v>
       </c>
       <c r="J23" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K23"/>
       <c r="L23"/>
@@ -3169,7 +3095,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B24">
         <v>0.7</v>
@@ -3178,14 +3104,14 @@
         <v>0.9</v>
       </c>
       <c r="D24" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E24"/>
       <c r="F24" s="8" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="H24" t="s">
         <v>14</v>
@@ -3194,7 +3120,7 @@
         <v>0.05</v>
       </c>
       <c r="J24" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K24"/>
       <c r="L24"/>
@@ -3224,7 +3150,7 @@
       <c r="D26"/>
       <c r="E26"/>
       <c r="F26" s="7" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="G26"/>
       <c r="H26"/>
@@ -3237,7 +3163,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B27">
         <v>40</v>
@@ -3249,13 +3175,13 @@
         <v>5</v>
       </c>
       <c r="E27" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="H27" t="s">
         <v>14</v>
@@ -3264,7 +3190,7 @@
         <v>1</v>
       </c>
       <c r="J27" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K27"/>
       <c r="L27"/>
@@ -3273,7 +3199,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B28">
         <v>26</v>
@@ -3285,13 +3211,13 @@
         <v>5</v>
       </c>
       <c r="E28" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="H28" t="s">
         <v>14</v>
@@ -3300,7 +3226,7 @@
         <v>1</v>
       </c>
       <c r="J28" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K28"/>
       <c r="L28"/>
@@ -3309,7 +3235,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B29">
         <v>4</v>
@@ -3321,13 +3247,13 @@
         <v>5</v>
       </c>
       <c r="E29" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="H29" t="s">
         <v>14</v>
@@ -3336,7 +3262,7 @@
         <v>1</v>
       </c>
       <c r="J29" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K29"/>
       <c r="L29"/>
@@ -3345,7 +3271,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="B30">
         <v>0.3</v>
@@ -3354,14 +3280,14 @@
         <v>0.7</v>
       </c>
       <c r="D30" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E30"/>
       <c r="F30" s="8" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="H30" t="s">
         <v>14</v>
@@ -3370,7 +3296,7 @@
         <v>0.1</v>
       </c>
       <c r="J30" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K30"/>
       <c r="L30"/>
@@ -3379,7 +3305,7 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B31">
         <v>0.2</v>
@@ -3388,14 +3314,14 @@
         <v>0.6</v>
       </c>
       <c r="D31" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E31"/>
       <c r="F31" s="8" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="H31" t="s">
         <v>14</v>
@@ -3404,7 +3330,7 @@
         <v>0.1</v>
       </c>
       <c r="J31" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K31"/>
       <c r="L31"/>
@@ -3413,7 +3339,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B32">
         <v>0.8</v>
@@ -3426,10 +3352,10 @@
       </c>
       <c r="E32"/>
       <c r="F32" s="8" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="H32" t="s">
         <v>14</v>
@@ -3438,7 +3364,7 @@
         <v>0.05</v>
       </c>
       <c r="J32" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K32"/>
       <c r="L32"/>
@@ -3571,13 +3497,13 @@
         <v>5</v>
       </c>
       <c r="E2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="H2" t="s">
         <v>14</v>
@@ -3586,7 +3512,7 @@
         <v>5</v>
       </c>
       <c r="J2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K2"/>
     </row>
@@ -3604,14 +3530,14 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F3" t="s">
         <v>80</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>83</v>
       </c>
-      <c r="G3" t="s">
-        <v>86</v>
-      </c>
       <c r="H3" t="s">
         <v>14</v>
       </c>
@@ -3619,7 +3545,7 @@
         <v>5</v>
       </c>
       <c r="J3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K3"/>
     </row>
@@ -3637,14 +3563,14 @@
         <v>5</v>
       </c>
       <c r="E4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G4" t="s">
         <v>84</v>
       </c>
-      <c r="G4" t="s">
-        <v>87</v>
-      </c>
       <c r="H4" t="s">
         <v>14</v>
       </c>
@@ -3652,7 +3578,7 @@
         <v>5</v>
       </c>
       <c r="J4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K4"/>
     </row>
@@ -3670,14 +3596,14 @@
         <v>5</v>
       </c>
       <c r="E5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G5" t="s">
         <v>85</v>
       </c>
-      <c r="G5" t="s">
-        <v>88</v>
-      </c>
       <c r="H5" t="s">
         <v>14</v>
       </c>
@@ -3685,7 +3611,7 @@
         <v>5</v>
       </c>
       <c r="J5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K5"/>
     </row>
@@ -3703,13 +3629,13 @@
         <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="H6" t="s">
         <v>14</v>
@@ -3718,7 +3644,7 @@
         <v>0.1</v>
       </c>
       <c r="J6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K6"/>
     </row>
@@ -3737,10 +3663,10 @@
       </c>
       <c r="E7"/>
       <c r="F7" s="8" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="H7" t="s">
         <v>14</v>
@@ -3749,7 +3675,7 @@
         <v>0.1</v>
       </c>
       <c r="J7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K7"/>
     </row>
@@ -3768,10 +3694,10 @@
       </c>
       <c r="E8"/>
       <c r="F8" s="8" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="H8" t="s">
         <v>14</v>
@@ -3780,7 +3706,7 @@
         <v>0.1</v>
       </c>
       <c r="J8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K8"/>
     </row>
@@ -3799,10 +3725,10 @@
       </c>
       <c r="E9"/>
       <c r="F9" s="8" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="H9" t="s">
         <v>14</v>
@@ -3811,7 +3737,7 @@
         <v>0.1</v>
       </c>
       <c r="J9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K9"/>
     </row>
@@ -3830,10 +3756,10 @@
       </c>
       <c r="E10"/>
       <c r="F10" s="8" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H10" t="s">
         <v>14</v>
@@ -3842,13 +3768,13 @@
         <v>0.1</v>
       </c>
       <c r="J10" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K10"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B11">
         <v>0.17</v>
@@ -3861,10 +3787,10 @@
       </c>
       <c r="E11"/>
       <c r="F11" s="8" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="H11" t="s">
         <v>14</v>
@@ -3873,13 +3799,13 @@
         <v>0.05</v>
       </c>
       <c r="J11" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="K11"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B12">
         <v>0.65</v>
@@ -3892,10 +3818,10 @@
       </c>
       <c r="E12"/>
       <c r="F12" s="8" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="H12" t="s">
         <v>14</v>
@@ -3904,13 +3830,13 @@
         <v>0.05</v>
       </c>
       <c r="J12" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="K12"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B13">
         <v>23</v>
@@ -3922,13 +3848,13 @@
         <v>5</v>
       </c>
       <c r="E13" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="H13" t="s">
         <v>14</v>
@@ -3937,13 +3863,13 @@
         <v>1</v>
       </c>
       <c r="J13" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="K13"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B14">
         <v>8</v>
@@ -3955,13 +3881,13 @@
         <v>5</v>
       </c>
       <c r="E14" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="H14" t="s">
         <v>14</v>
@@ -3970,13 +3896,13 @@
         <v>1</v>
       </c>
       <c r="J14" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="K14"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B15">
         <v>34</v>
@@ -3988,13 +3914,13 @@
         <v>5</v>
       </c>
       <c r="E15" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="H15" t="s">
         <v>14</v>
@@ -4003,13 +3929,13 @@
         <v>1</v>
       </c>
       <c r="J15" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="K15"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B16">
         <v>3</v>
@@ -4021,13 +3947,13 @@
         <v>5</v>
       </c>
       <c r="E16" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H16" t="s">
         <v>14</v>
@@ -4036,13 +3962,13 @@
         <v>1</v>
       </c>
       <c r="J16" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="K16"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B17">
         <v>9</v>
@@ -4054,13 +3980,13 @@
         <v>5</v>
       </c>
       <c r="E17" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="H17" t="s">
         <v>14</v>
@@ -4069,13 +3995,13 @@
         <v>1</v>
       </c>
       <c r="J17" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="K17"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -4087,13 +4013,13 @@
         <v>5</v>
       </c>
       <c r="E18" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="H18" t="s">
         <v>14</v>
@@ -4102,13 +4028,13 @@
         <v>1</v>
       </c>
       <c r="J18" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="K18"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B19">
         <v>0.8</v>
@@ -4120,13 +4046,13 @@
         <v>5</v>
       </c>
       <c r="E19" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="H19" t="s">
         <v>14</v>
@@ -4135,7 +4061,7 @@
         <v>0.1</v>
       </c>
       <c r="J19" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="K19"/>
     </row>

--- a/input_parameters_shiny.xlsx
+++ b/input_parameters_shiny.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pauld\Documents\Climate Impact Onions Forecast\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B34544A6-1801-4D69-BB99-0ABC198A65FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12B03AE3-E86B-46DF-843F-2DC6CE15E39E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" tabRatio="815" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="815" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet_names" sheetId="2" r:id="rId1"/>
@@ -115,18 +115,6 @@
     <t>LUE_onion_p</t>
   </si>
   <si>
-    <t>LAI_emergence_p</t>
-  </si>
-  <si>
-    <t>LAI_veg_p</t>
-  </si>
-  <si>
-    <t>LAI_bulbing_p</t>
-  </si>
-  <si>
-    <t>LAI_maturation_p</t>
-  </si>
-  <si>
     <t>onions_per_ha_p</t>
   </si>
   <si>
@@ -541,30 +529,6 @@
     <t>Biomasseproduktion pro Einheit eingestrahlter und genutzter Strahlung (g/MJ).</t>
   </si>
   <si>
-    <t>Blattflächenindex während der Auflaufphase.</t>
-  </si>
-  <si>
-    <t>Blattflächenindex während der vegetativen Wachstumsphase.</t>
-  </si>
-  <si>
-    <t>Blattflächenindex während der Knollenbildungsphase.</t>
-  </si>
-  <si>
-    <t>Blattflächenindex während der Reifephase.</t>
-  </si>
-  <si>
-    <t>Blattflächenindex Feldaufgang</t>
-  </si>
-  <si>
-    <t>Blattflächenindex vegetative Phase</t>
-  </si>
-  <si>
-    <t>Blattflächenindex Abreifephase</t>
-  </si>
-  <si>
-    <t>Blattflächenindex Knollenbildungsphase</t>
-  </si>
-  <si>
     <t>Standortkonstante Krs</t>
   </si>
   <si>
@@ -791,6 +755,42 @@
   </si>
   <si>
     <t>impact_rh_drought_t</t>
+  </si>
+  <si>
+    <t>leaf_area_em_per_plant_p</t>
+  </si>
+  <si>
+    <t>leaf_area_vg_per_plant_p</t>
+  </si>
+  <si>
+    <t>leaf_area_bl_per_plant_p</t>
+  </si>
+  <si>
+    <t>leaf_area_mt_per_plant_p</t>
+  </si>
+  <si>
+    <t>Blattfläche pro Pflanze Feldaufgang [cm²]</t>
+  </si>
+  <si>
+    <t>Blattfläche pro Pflanze vegetative Phase [cm²]</t>
+  </si>
+  <si>
+    <t>Blattfläche pro Pflanze Knollenbildungsphase [cm²]</t>
+  </si>
+  <si>
+    <t>Blattfläche pro Pflanze Abreifephase [cm²]</t>
+  </si>
+  <si>
+    <t>Blattfläche pro Pflanze während der Auflaufphase. [cm²]</t>
+  </si>
+  <si>
+    <t>Blattflächenindex während der vegetativen Wachstumsphase. [cm²]</t>
+  </si>
+  <si>
+    <t>Blattflächenindex während der Knollenbildungsphase. [cm²]</t>
+  </si>
+  <si>
+    <t>Blattflächenindex während der Reifephase. [cm²]</t>
   </si>
 </sst>
 </file>
@@ -1208,31 +1208,31 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B6" t="s">
         <v>10</v>
@@ -1300,10 +1300,10 @@
         <v>4</v>
       </c>
       <c r="F2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G2" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="H2" t="s">
         <v>14</v>
@@ -1326,10 +1326,10 @@
         <v>4</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>14</v>
@@ -1338,7 +1338,7 @@
         <v>100</v>
       </c>
       <c r="J3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1396,7 +1396,7 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="B2">
         <v>0.65</v>
@@ -1405,14 +1405,14 @@
         <v>0.85</v>
       </c>
       <c r="D2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E2"/>
       <c r="F2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="H2" t="s">
         <v>14</v>
@@ -1421,13 +1421,13 @@
         <v>0.1</v>
       </c>
       <c r="J2" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="K2"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B3">
         <v>700000</v>
@@ -1439,13 +1439,13 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H3" t="s">
         <v>14</v>
@@ -1454,13 +1454,13 @@
         <v>0.1</v>
       </c>
       <c r="J3" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="K3"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="B4">
         <v>0.88</v>
@@ -1469,14 +1469,14 @@
         <v>0.92</v>
       </c>
       <c r="D4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E4"/>
       <c r="F4" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="G4" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="H4" t="s">
         <v>14</v>
@@ -1485,13 +1485,13 @@
         <v>0.05</v>
       </c>
       <c r="J4" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="K4"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -1503,13 +1503,13 @@
         <v>5</v>
       </c>
       <c r="E5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F5" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="G5" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="H5" t="s">
         <v>14</v>
@@ -1518,12 +1518,12 @@
         <v>0.5</v>
       </c>
       <c r="J5" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -1535,13 +1535,13 @@
         <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F6" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="G6" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="H6" t="s">
         <v>14</v>
@@ -1550,12 +1550,12 @@
         <v>1</v>
       </c>
       <c r="J6" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="B7">
         <v>2</v>
@@ -1567,13 +1567,13 @@
         <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F7" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="G7" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="H7" t="s">
         <v>14</v>
@@ -1582,12 +1582,12 @@
         <v>1</v>
       </c>
       <c r="J7" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="B8">
         <v>6</v>
@@ -1599,13 +1599,13 @@
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="F8" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="G8" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="H8" t="s">
         <v>14</v>
@@ -1614,12 +1614,12 @@
         <v>1</v>
       </c>
       <c r="J8" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="B9">
         <v>3</v>
@@ -1631,13 +1631,13 @@
         <v>4</v>
       </c>
       <c r="E9" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F9" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="G9" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="H9" t="s">
         <v>14</v>
@@ -1646,12 +1646,12 @@
         <v>1</v>
       </c>
       <c r="J9" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="B10">
         <v>45</v>
@@ -1663,13 +1663,13 @@
         <v>4</v>
       </c>
       <c r="E10" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="F10" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="G10" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="H10" t="s">
         <v>14</v>
@@ -1678,12 +1678,12 @@
         <v>1</v>
       </c>
       <c r="J10" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="B11">
         <v>100</v>
@@ -1695,13 +1695,13 @@
         <v>4</v>
       </c>
       <c r="E11" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="F11" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="G11" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="H11" t="s">
         <v>14</v>
@@ -1710,7 +1710,7 @@
         <v>1</v>
       </c>
       <c r="J11" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -1973,15 +1973,15 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F2" s="4" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B3">
         <v>25</v>
@@ -1993,13 +1993,13 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="H3" t="s">
         <v>14</v>
@@ -2008,7 +2008,7 @@
         <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="K3"/>
       <c r="L3"/>
@@ -2016,7 +2016,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B4">
         <v>45</v>
@@ -2028,13 +2028,13 @@
         <v>5</v>
       </c>
       <c r="E4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="H4" t="s">
         <v>14</v>
@@ -2043,7 +2043,7 @@
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="K4"/>
       <c r="L4"/>
@@ -2051,7 +2051,7 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B5">
         <v>0.3</v>
@@ -2060,14 +2060,14 @@
         <v>0.8</v>
       </c>
       <c r="D5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E5"/>
       <c r="F5" s="8" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="H5" t="s">
         <v>14</v>
@@ -2076,7 +2076,7 @@
         <v>0.1</v>
       </c>
       <c r="J5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="K5"/>
       <c r="L5"/>
@@ -2084,7 +2084,7 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B6">
         <v>0.6</v>
@@ -2093,14 +2093,14 @@
         <v>0.85</v>
       </c>
       <c r="D6" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E6"/>
       <c r="F6" s="8" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="H6" t="s">
         <v>14</v>
@@ -2109,7 +2109,7 @@
         <v>0.05</v>
       </c>
       <c r="J6" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="K6"/>
       <c r="L6"/>
@@ -2117,12 +2117,12 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F8" s="4" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B9">
         <v>20</v>
@@ -2134,13 +2134,13 @@
         <v>5</v>
       </c>
       <c r="E9" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="H9" t="s">
         <v>14</v>
@@ -2149,7 +2149,7 @@
         <v>1</v>
       </c>
       <c r="J9" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="K9"/>
       <c r="L9"/>
@@ -2158,7 +2158,7 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B10">
         <v>18</v>
@@ -2170,13 +2170,13 @@
         <v>5</v>
       </c>
       <c r="E10" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="H10" t="s">
         <v>14</v>
@@ -2185,7 +2185,7 @@
         <v>1</v>
       </c>
       <c r="J10" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="K10"/>
       <c r="L10"/>
@@ -2194,7 +2194,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B11">
         <v>0.3</v>
@@ -2203,14 +2203,14 @@
         <v>0.8</v>
       </c>
       <c r="D11" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E11"/>
       <c r="F11" s="8" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="H11" t="s">
         <v>14</v>
@@ -2219,7 +2219,7 @@
         <v>0.1</v>
       </c>
       <c r="J11" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="K11"/>
       <c r="L11"/>
@@ -2228,7 +2228,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="B12">
         <v>0.5</v>
@@ -2237,14 +2237,14 @@
         <v>0.8</v>
       </c>
       <c r="D12" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E12"/>
       <c r="F12" s="8" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="H12" t="s">
         <v>14</v>
@@ -2253,7 +2253,7 @@
         <v>0.05</v>
       </c>
       <c r="J12" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="K12"/>
       <c r="L12"/>
@@ -2262,12 +2262,12 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F14" s="6" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="B15">
         <v>85</v>
@@ -2279,13 +2279,13 @@
         <v>5</v>
       </c>
       <c r="E15" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="H15" t="s">
         <v>14</v>
@@ -2294,12 +2294,12 @@
         <v>1</v>
       </c>
       <c r="J15" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B16">
         <v>24</v>
@@ -2311,13 +2311,13 @@
         <v>5</v>
       </c>
       <c r="E16" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="H16" t="s">
         <v>14</v>
@@ -2326,12 +2326,12 @@
         <v>1</v>
       </c>
       <c r="J16" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="B17">
         <v>0.5</v>
@@ -2340,14 +2340,14 @@
         <v>0.6</v>
       </c>
       <c r="D17" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E17"/>
       <c r="F17" s="8" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="H17" t="s">
         <v>14</v>
@@ -2356,12 +2356,12 @@
         <v>0.1</v>
       </c>
       <c r="J17" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B18">
         <v>0.6</v>
@@ -2370,14 +2370,14 @@
         <v>0.7</v>
       </c>
       <c r="D18" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E18"/>
       <c r="F18" s="8" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="H18" t="s">
         <v>14</v>
@@ -2386,12 +2386,12 @@
         <v>0.05</v>
       </c>
       <c r="J18" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B19">
         <v>0.2</v>
@@ -2400,16 +2400,16 @@
         <v>0.3</v>
       </c>
       <c r="D19" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E19" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="H19" t="s">
         <v>14</v>
@@ -2418,12 +2418,12 @@
         <v>0.5</v>
       </c>
       <c r="J19" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B20">
         <v>0.6</v>
@@ -2432,14 +2432,14 @@
         <v>0.9</v>
       </c>
       <c r="D20" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E20"/>
       <c r="F20" s="8" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="H20" t="s">
         <v>14</v>
@@ -2448,7 +2448,7 @@
         <v>0.05</v>
       </c>
       <c r="J20" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -2525,15 +2525,15 @@
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="F2" s="4" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="B3">
         <v>85</v>
@@ -2545,13 +2545,13 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F3" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="G3" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="H3" t="s">
         <v>14</v>
@@ -2560,12 +2560,12 @@
         <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B4">
         <v>15</v>
@@ -2577,13 +2577,13 @@
         <v>5</v>
       </c>
       <c r="E4" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F4" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="G4" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="H4" t="s">
         <v>14</v>
@@ -2592,12 +2592,12 @@
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="B5">
         <v>3</v>
@@ -2609,13 +2609,13 @@
         <v>5</v>
       </c>
       <c r="E5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F5" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="G5" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="H5" t="s">
         <v>14</v>
@@ -2624,12 +2624,12 @@
         <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="B6">
         <v>0.4</v>
@@ -2638,14 +2638,14 @@
         <v>0.6</v>
       </c>
       <c r="D6" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E6"/>
       <c r="F6" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="G6" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="H6" t="s">
         <v>14</v>
@@ -2654,12 +2654,12 @@
         <v>0.1</v>
       </c>
       <c r="J6" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B7">
         <v>0.5</v>
@@ -2668,14 +2668,14 @@
         <v>0.7</v>
       </c>
       <c r="D7" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E7"/>
       <c r="F7" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="G7" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="H7" t="s">
         <v>14</v>
@@ -2684,12 +2684,12 @@
         <v>0.1</v>
       </c>
       <c r="J7" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B8">
         <v>0.6</v>
@@ -2698,14 +2698,14 @@
         <v>0.8</v>
       </c>
       <c r="D8" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E8"/>
       <c r="F8" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G8" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H8" t="s">
         <v>14</v>
@@ -2714,7 +2714,7 @@
         <v>0.05</v>
       </c>
       <c r="J8" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -2722,13 +2722,13 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F10" s="5" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="J10"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="B11">
         <v>85</v>
@@ -2740,13 +2740,13 @@
         <v>5</v>
       </c>
       <c r="E11" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F11" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="G11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="H11" t="s">
         <v>14</v>
@@ -2755,12 +2755,12 @@
         <v>1</v>
       </c>
       <c r="J11" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B12">
         <v>16</v>
@@ -2772,13 +2772,13 @@
         <v>5</v>
       </c>
       <c r="E12" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F12" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="G12" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="H12" t="s">
         <v>14</v>
@@ -2787,12 +2787,12 @@
         <v>1</v>
       </c>
       <c r="J12" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B13">
         <v>3</v>
@@ -2804,13 +2804,13 @@
         <v>5</v>
       </c>
       <c r="E13" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="G13" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="H13" t="s">
         <v>14</v>
@@ -2819,12 +2819,12 @@
         <v>1</v>
       </c>
       <c r="J13" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="B14">
         <v>0.4</v>
@@ -2833,16 +2833,16 @@
         <v>0.6</v>
       </c>
       <c r="D14" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E14" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F14" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="G14" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="H14" t="s">
         <v>14</v>
@@ -2851,12 +2851,12 @@
         <v>0.1</v>
       </c>
       <c r="J14" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B15">
         <v>0.3</v>
@@ -2865,14 +2865,14 @@
         <v>0.5</v>
       </c>
       <c r="D15" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E15"/>
       <c r="F15" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G15" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="H15" t="s">
         <v>14</v>
@@ -2881,12 +2881,12 @@
         <v>0.1</v>
       </c>
       <c r="J15" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B16">
         <v>0.6</v>
@@ -2899,10 +2899,10 @@
       </c>
       <c r="E16"/>
       <c r="F16" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G16" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H16" t="s">
         <v>14</v>
@@ -2911,7 +2911,7 @@
         <v>0.05</v>
       </c>
       <c r="J16" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
@@ -2919,13 +2919,13 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F18" s="6" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="J18"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -2937,13 +2937,13 @@
         <v>5</v>
       </c>
       <c r="E19" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F19" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="H19" t="s">
         <v>14</v>
@@ -2952,12 +2952,12 @@
         <v>1</v>
       </c>
       <c r="J19" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="B20">
         <v>22</v>
@@ -2969,13 +2969,13 @@
         <v>5</v>
       </c>
       <c r="E20" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="H20" t="s">
         <v>14</v>
@@ -2984,7 +2984,7 @@
         <v>1</v>
       </c>
       <c r="J20" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="K20"/>
       <c r="L20"/>
@@ -2993,7 +2993,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="B21">
         <v>4</v>
@@ -3005,13 +3005,13 @@
         <v>5</v>
       </c>
       <c r="E21" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="H21" t="s">
         <v>14</v>
@@ -3020,7 +3020,7 @@
         <v>1</v>
       </c>
       <c r="J21" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="K21"/>
       <c r="L21"/>
@@ -3029,7 +3029,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="B22">
         <v>0.3</v>
@@ -3038,16 +3038,16 @@
         <v>0.7</v>
       </c>
       <c r="D22" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E22" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="H22" t="s">
         <v>14</v>
@@ -3056,12 +3056,12 @@
         <v>0.1</v>
       </c>
       <c r="J22" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B23">
         <v>0.2</v>
@@ -3070,14 +3070,14 @@
         <v>0.6</v>
       </c>
       <c r="D23" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E23"/>
       <c r="F23" s="8" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="H23" t="s">
         <v>14</v>
@@ -3086,7 +3086,7 @@
         <v>0.1</v>
       </c>
       <c r="J23" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="K23"/>
       <c r="L23"/>
@@ -3095,7 +3095,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B24">
         <v>0.7</v>
@@ -3104,14 +3104,14 @@
         <v>0.9</v>
       </c>
       <c r="D24" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E24"/>
       <c r="F24" s="8" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H24" t="s">
         <v>14</v>
@@ -3120,7 +3120,7 @@
         <v>0.05</v>
       </c>
       <c r="J24" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="K24"/>
       <c r="L24"/>
@@ -3150,7 +3150,7 @@
       <c r="D26"/>
       <c r="E26"/>
       <c r="F26" s="7" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G26"/>
       <c r="H26"/>
@@ -3163,7 +3163,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="B27">
         <v>40</v>
@@ -3175,13 +3175,13 @@
         <v>5</v>
       </c>
       <c r="E27" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="H27" t="s">
         <v>14</v>
@@ -3190,7 +3190,7 @@
         <v>1</v>
       </c>
       <c r="J27" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="K27"/>
       <c r="L27"/>
@@ -3199,7 +3199,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B28">
         <v>26</v>
@@ -3211,13 +3211,13 @@
         <v>5</v>
       </c>
       <c r="E28" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H28" t="s">
         <v>14</v>
@@ -3226,7 +3226,7 @@
         <v>1</v>
       </c>
       <c r="J28" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="K28"/>
       <c r="L28"/>
@@ -3235,7 +3235,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B29">
         <v>4</v>
@@ -3247,13 +3247,13 @@
         <v>5</v>
       </c>
       <c r="E29" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="H29" t="s">
         <v>14</v>
@@ -3262,7 +3262,7 @@
         <v>1</v>
       </c>
       <c r="J29" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="K29"/>
       <c r="L29"/>
@@ -3271,7 +3271,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="B30">
         <v>0.3</v>
@@ -3280,14 +3280,14 @@
         <v>0.7</v>
       </c>
       <c r="D30" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E30"/>
       <c r="F30" s="8" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="H30" t="s">
         <v>14</v>
@@ -3296,7 +3296,7 @@
         <v>0.1</v>
       </c>
       <c r="J30" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="K30"/>
       <c r="L30"/>
@@ -3305,7 +3305,7 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B31">
         <v>0.2</v>
@@ -3314,14 +3314,14 @@
         <v>0.6</v>
       </c>
       <c r="D31" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E31"/>
       <c r="F31" s="8" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="H31" t="s">
         <v>14</v>
@@ -3330,7 +3330,7 @@
         <v>0.1</v>
       </c>
       <c r="J31" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="K31"/>
       <c r="L31"/>
@@ -3339,7 +3339,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B32">
         <v>0.8</v>
@@ -3352,10 +3352,10 @@
       </c>
       <c r="E32"/>
       <c r="F32" s="8" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="H32" t="s">
         <v>14</v>
@@ -3364,7 +3364,7 @@
         <v>0.05</v>
       </c>
       <c r="J32" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="K32"/>
       <c r="L32"/>
@@ -3497,13 +3497,13 @@
         <v>5</v>
       </c>
       <c r="E2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H2" t="s">
         <v>14</v>
@@ -3512,7 +3512,7 @@
         <v>5</v>
       </c>
       <c r="J2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="K2"/>
     </row>
@@ -3530,13 +3530,13 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G3" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="H3" t="s">
         <v>14</v>
@@ -3545,7 +3545,7 @@
         <v>5</v>
       </c>
       <c r="J3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="K3"/>
     </row>
@@ -3563,13 +3563,13 @@
         <v>5</v>
       </c>
       <c r="E4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F4" t="s">
         <v>77</v>
       </c>
-      <c r="F4" t="s">
-        <v>81</v>
-      </c>
       <c r="G4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="H4" t="s">
         <v>14</v>
@@ -3578,7 +3578,7 @@
         <v>5</v>
       </c>
       <c r="J4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="K4"/>
     </row>
@@ -3596,13 +3596,13 @@
         <v>5</v>
       </c>
       <c r="E5" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F5" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="G5" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="H5" t="s">
         <v>14</v>
@@ -3611,7 +3611,7 @@
         <v>5</v>
       </c>
       <c r="J5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="K5"/>
     </row>
@@ -3629,13 +3629,13 @@
         <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H6" t="s">
         <v>14</v>
@@ -3644,13 +3644,13 @@
         <v>0.1</v>
       </c>
       <c r="J6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="K6"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="B7">
         <v>0.2</v>
@@ -3663,10 +3663,10 @@
       </c>
       <c r="E7"/>
       <c r="F7" s="8" t="s">
-        <v>171</v>
+        <v>243</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>167</v>
+        <v>247</v>
       </c>
       <c r="H7" t="s">
         <v>14</v>
@@ -3675,13 +3675,13 @@
         <v>0.1</v>
       </c>
       <c r="J7" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="K7"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>240</v>
       </c>
       <c r="B8">
         <v>1.1000000000000001</v>
@@ -3694,10 +3694,10 @@
       </c>
       <c r="E8"/>
       <c r="F8" s="8" t="s">
-        <v>172</v>
+        <v>244</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>168</v>
+        <v>248</v>
       </c>
       <c r="H8" t="s">
         <v>14</v>
@@ -3706,13 +3706,13 @@
         <v>0.1</v>
       </c>
       <c r="J8" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="K8"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>241</v>
       </c>
       <c r="B9">
         <v>2</v>
@@ -3725,10 +3725,10 @@
       </c>
       <c r="E9"/>
       <c r="F9" s="8" t="s">
-        <v>174</v>
+        <v>245</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>169</v>
+        <v>249</v>
       </c>
       <c r="H9" t="s">
         <v>14</v>
@@ -3737,13 +3737,13 @@
         <v>0.1</v>
       </c>
       <c r="J9" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="K9"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>28</v>
+        <v>242</v>
       </c>
       <c r="B10">
         <v>1.4</v>
@@ -3756,10 +3756,10 @@
       </c>
       <c r="E10"/>
       <c r="F10" s="8" t="s">
-        <v>173</v>
+        <v>246</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>170</v>
+        <v>250</v>
       </c>
       <c r="H10" t="s">
         <v>14</v>
@@ -3768,13 +3768,13 @@
         <v>0.1</v>
       </c>
       <c r="J10" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="K10"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B11">
         <v>0.17</v>
@@ -3787,10 +3787,10 @@
       </c>
       <c r="E11"/>
       <c r="F11" s="8" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="H11" t="s">
         <v>14</v>
@@ -3799,13 +3799,13 @@
         <v>0.05</v>
       </c>
       <c r="J11" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="K11"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B12">
         <v>0.65</v>
@@ -3818,10 +3818,10 @@
       </c>
       <c r="E12"/>
       <c r="F12" s="8" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="H12" t="s">
         <v>14</v>
@@ -3830,13 +3830,13 @@
         <v>0.05</v>
       </c>
       <c r="J12" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="K12"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B13">
         <v>23</v>
@@ -3848,13 +3848,13 @@
         <v>5</v>
       </c>
       <c r="E13" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="H13" t="s">
         <v>14</v>
@@ -3863,13 +3863,13 @@
         <v>1</v>
       </c>
       <c r="J13" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="K13"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B14">
         <v>8</v>
@@ -3881,13 +3881,13 @@
         <v>5</v>
       </c>
       <c r="E14" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="H14" t="s">
         <v>14</v>
@@ -3896,13 +3896,13 @@
         <v>1</v>
       </c>
       <c r="J14" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="K14"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B15">
         <v>34</v>
@@ -3914,13 +3914,13 @@
         <v>5</v>
       </c>
       <c r="E15" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="H15" t="s">
         <v>14</v>
@@ -3929,13 +3929,13 @@
         <v>1</v>
       </c>
       <c r="J15" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="K15"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B16">
         <v>3</v>
@@ -3947,13 +3947,13 @@
         <v>5</v>
       </c>
       <c r="E16" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="H16" t="s">
         <v>14</v>
@@ -3962,13 +3962,13 @@
         <v>1</v>
       </c>
       <c r="J16" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="K16"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B17">
         <v>9</v>
@@ -3980,13 +3980,13 @@
         <v>5</v>
       </c>
       <c r="E17" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="H17" t="s">
         <v>14</v>
@@ -3995,13 +3995,13 @@
         <v>1</v>
       </c>
       <c r="J17" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="K17"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -4013,13 +4013,13 @@
         <v>5</v>
       </c>
       <c r="E18" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="H18" t="s">
         <v>14</v>
@@ -4028,13 +4028,13 @@
         <v>1</v>
       </c>
       <c r="J18" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="K18"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B19">
         <v>0.8</v>
@@ -4046,13 +4046,13 @@
         <v>5</v>
       </c>
       <c r="E19" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="H19" t="s">
         <v>14</v>
@@ -4061,7 +4061,7 @@
         <v>0.1</v>
       </c>
       <c r="J19" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="K19"/>
     </row>

--- a/input_parameters_shiny.xlsx
+++ b/input_parameters_shiny.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pauld\Downloads\Telegram Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pauld\Documents\Climate Impact Onions Forecast\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09236FEF-3D38-41D2-9086-DA85B19D7102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F762E86-8D40-4D10-A7BC-3A6FB25A51DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet_names" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="256">
   <si>
     <t>sheet_names</t>
   </si>
@@ -794,6 +794,18 @@
   </si>
   <si>
     <t>Gewichtungsfaktor (0–1), der angibt, wie stark aufeinanderfolgende trockene Tage das Risiko beeinflussen.</t>
+  </si>
+  <si>
+    <t>nfk_mm_per_cm_t</t>
+  </si>
+  <si>
+    <t>mm cm⁻¹</t>
+  </si>
+  <si>
+    <t>Pflanzenverfügbare Nutzbare Feldkapazität pro cm Wurzeltiefe. Bestimmt TAW</t>
+  </si>
+  <si>
+    <t>Dieser Parameter gibt an, wie viele Millimeter Wasser pro Zentimeter Wurzelzone vom Boden für die Pflanze verfügbar sind – also wie viel Wasser der Boden speichern kann, das die Zwiebel auch wirklich aufnehmen kann.</t>
   </si>
 </sst>
 </file>
@@ -856,25 +868,20 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
@@ -1184,8 +1191,7 @@
   <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.85546875" style="2" customWidth="1"/>
-    <col min="2" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="29.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -1197,42 +1203,42 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="A6" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1279,32 +1285,32 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="B2" s="9">
+      <c r="B2" s="6">
         <v>1000</v>
       </c>
-      <c r="C2" s="9">
+      <c r="C2" s="6">
         <v>1000</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9" t="s">
+      <c r="E2" s="6"/>
+      <c r="F2" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="9">
+      <c r="I2" s="6">
         <v>100</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="5" t="s">
         <v>244</v>
       </c>
     </row>
@@ -1351,354 +1357,354 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2">
         <v>200</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2">
         <v>300</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" t="s">
         <v>30</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" t="s">
         <v>31</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I2" s="2">
+      <c r="H2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I2">
         <v>10</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="A3" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3">
         <v>900</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3">
         <v>1100</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
         <v>29</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" t="s">
         <v>34</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" t="s">
         <v>35</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I3" s="2">
+      <c r="H3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3">
         <v>10</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="A4" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4">
         <v>1400</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4">
         <v>1500</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
         <v>29</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" t="s">
         <v>37</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" t="s">
         <v>38</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I4" s="2">
+      <c r="H4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4">
         <v>10</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="A5" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5">
         <v>1800</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5">
         <v>2000</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" t="s">
         <v>40</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" t="s">
         <v>41</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I5" s="2">
+      <c r="H5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5">
         <v>10</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="J5" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="A6" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6">
         <v>50</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6">
         <v>150</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="D6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" t="s">
         <v>43</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" t="s">
         <v>44</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" t="s">
         <v>45</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I6" s="2">
+      <c r="H6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6">
         <v>5</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="J6" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="A7" t="s">
         <v>46</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7">
         <v>150</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7">
         <v>350</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" t="s">
         <v>43</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" t="s">
         <v>47</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" t="s">
         <v>48</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I7" s="2">
+      <c r="H7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7">
         <v>5</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="J7" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="A8" t="s">
         <v>49</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8">
         <v>300</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8">
         <v>600</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="D8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" t="s">
         <v>43</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" t="s">
         <v>50</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" t="s">
         <v>51</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I8" s="2">
+      <c r="H8" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8">
         <v>5</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="J8" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="A9" t="s">
         <v>52</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9">
         <v>200</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9">
         <v>400</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="D9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" t="s">
         <v>53</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" t="s">
         <v>54</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I9" s="2">
+      <c r="H9" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9">
         <v>5</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="J9" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="A10" t="s">
         <v>55</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10">
         <v>0.65</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10">
         <v>0.85</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" t="s">
         <v>56</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" t="s">
         <v>57</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" t="s">
         <v>58</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G10" t="s">
         <v>204</v>
       </c>
-      <c r="H10" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I10" s="2">
+      <c r="H10" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10">
         <v>0.05</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="J10" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="A11" t="s">
         <v>59</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11">
         <v>700000</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11">
         <v>900000</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="D11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" t="s">
         <v>60</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" t="s">
         <v>61</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G11" t="s">
         <v>62</v>
       </c>
-      <c r="H11" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I11" s="2">
+      <c r="H11" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11">
         <v>10000</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="J11" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="A12" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12">
         <v>45</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12">
         <v>135</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="D12" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" t="s">
         <v>24</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" t="s">
         <v>25</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="G12" t="s">
         <v>26</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="H12" t="s">
         <v>27</v>
       </c>
-      <c r="I12" s="2">
+      <c r="I12">
         <v>1</v>
       </c>
-      <c r="J12" s="2" t="s">
+      <c r="J12" t="s">
         <v>206</v>
       </c>
     </row>
@@ -1712,10 +1718,8 @@
   <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.42578125" style="2" customWidth="1"/>
-    <col min="2" max="5" width="9.140625" style="2"/>
-    <col min="6" max="6" width="39.28515625" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="36.42578125" customWidth="1"/>
+    <col min="6" max="6" width="39.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1765,432 +1769,432 @@
       <c r="J2" s="1"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="A3" t="s">
         <v>72</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="2">
         <v>25</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="2">
         <v>35</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
         <v>64</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I3" s="2">
+      <c r="H3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3">
         <v>1</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="A4" t="s">
         <v>73</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="2">
         <v>45</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="2">
         <v>60</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
         <v>64</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I4" s="2">
+      <c r="H4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4">
         <v>1</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="A5" t="s">
         <v>207</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="4">
         <v>0.8</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" t="s">
         <v>56</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I5" s="2">
+      <c r="H5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5">
         <v>0.1</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="J5" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="A6" t="s">
         <v>74</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="4">
         <v>0.85</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" t="s">
         <v>56</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" t="s">
         <v>57</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" t="s">
         <v>75</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" t="s">
         <v>224</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I6" s="2">
+      <c r="H6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6">
         <v>0.05</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="J6" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B7" s="3"/>
-      <c r="C7" s="5"/>
-      <c r="F7" s="6" t="s">
+      <c r="B7" s="2"/>
+      <c r="C7" s="4"/>
+      <c r="F7" s="3" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="A8" t="s">
         <v>63</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="2">
         <v>20</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="2">
         <v>40</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="D8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" t="s">
         <v>64</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" t="s">
         <v>65</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" t="s">
         <v>66</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I8" s="2">
+      <c r="H8" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8">
         <v>1</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="J8" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="A9" t="s">
         <v>67</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="2">
         <v>18</v>
       </c>
-      <c r="C9" s="3">
-        <v>23</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="C9" s="2">
+        <v>23</v>
+      </c>
+      <c r="D9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" t="s">
         <v>68</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" t="s">
         <v>69</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" t="s">
         <v>70</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I9" s="2">
+      <c r="H9" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9">
         <v>1</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="J9" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="A10" t="s">
         <v>210</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="2">
         <v>0.5</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" t="s">
         <v>56</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" t="s">
         <v>219</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G10" t="s">
         <v>220</v>
       </c>
-      <c r="H10" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I10" s="2">
+      <c r="H10" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10">
         <v>0.1</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="J10" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="A11" t="s">
         <v>71</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11" s="4">
         <v>0.85</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" t="s">
         <v>56</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" t="s">
         <v>223</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G11" t="s">
         <v>225</v>
       </c>
-      <c r="H11" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I11" s="2">
+      <c r="H11" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11">
         <v>0.05</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="J11" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B12" s="3"/>
-      <c r="C12" s="5"/>
-      <c r="F12" s="7" t="s">
+      <c r="B12" s="2"/>
+      <c r="C12" s="4"/>
+      <c r="F12" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+      <c r="A13" t="s">
         <v>76</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="2">
         <v>30</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="2">
         <v>33</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="D13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" t="s">
         <v>68</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F13" t="s">
         <v>77</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" t="s">
         <v>78</v>
       </c>
-      <c r="H13" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I13" s="2">
+      <c r="H13" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13">
         <v>1</v>
       </c>
-      <c r="J13" s="2" t="s">
+      <c r="J13" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+      <c r="A14" t="s">
         <v>79</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="4">
         <v>0.8</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" t="s">
         <v>56</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="G14" t="s">
         <v>231</v>
       </c>
-      <c r="H14" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I14" s="2">
+      <c r="H14" t="s">
+        <v>32</v>
+      </c>
+      <c r="I14">
         <v>0.1</v>
       </c>
-      <c r="J14" s="2" t="s">
+      <c r="J14" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+      <c r="A15" t="s">
         <v>81</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="C15" s="5">
+      <c r="C15" s="4">
         <v>0.8</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" t="s">
         <v>56</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="G15" t="s">
         <v>232</v>
       </c>
-      <c r="H15" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I15" s="2">
+      <c r="H15" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15">
         <v>0.1</v>
       </c>
-      <c r="J15" s="2" t="s">
+      <c r="J15" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+      <c r="A16" t="s">
         <v>136</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C16" s="4">
         <v>0.2</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" t="s">
         <v>56</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F16" t="s">
         <v>221</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="G16" t="s">
         <v>222</v>
       </c>
-      <c r="H16" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I16" s="2">
+      <c r="H16" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16">
         <v>0.05</v>
       </c>
-      <c r="J16" s="2" t="s">
+      <c r="J16" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="3"/>
-      <c r="C19" s="5"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="4"/>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" s="3"/>
-      <c r="C20" s="5"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="4"/>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B24" s="3"/>
-      <c r="C24" s="5"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="4"/>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B26" s="3"/>
-      <c r="C26" s="5"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="4"/>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B27" s="3"/>
-      <c r="C27" s="5"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="4"/>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B28" s="3"/>
-      <c r="C28" s="5"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2199,14 +2203,14 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:N29"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
     <col min="6" max="6" width="36.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
@@ -2238,12 +2242,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F2" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>97</v>
       </c>
@@ -2271,15 +2275,11 @@
       <c r="I3">
         <v>1</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" t="s">
         <v>206</v>
       </c>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>102</v>
       </c>
@@ -2307,11 +2307,11 @@
       <c r="I4">
         <v>1</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>105</v>
       </c>
@@ -2339,11 +2339,11 @@
       <c r="I5">
         <v>1</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="J5" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>100</v>
       </c>
@@ -2356,10 +2356,10 @@
       <c r="D6" t="s">
         <v>56</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="3" t="s">
         <v>248</v>
       </c>
       <c r="H6" t="s">
@@ -2368,11 +2368,11 @@
       <c r="I6">
         <v>0.1</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="J6" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>101</v>
       </c>
@@ -2388,10 +2388,10 @@
       <c r="E7" t="s">
         <v>82</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="3" t="s">
         <v>249</v>
       </c>
       <c r="H7" t="s">
@@ -2400,11 +2400,11 @@
       <c r="I7">
         <v>1</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="J7" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>108</v>
       </c>
@@ -2429,17 +2429,16 @@
       <c r="I8">
         <v>0.05</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="J8" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F9" t="s">
         <v>234</v>
       </c>
-      <c r="J9" s="2"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>110</v>
       </c>
@@ -2467,11 +2466,11 @@
       <c r="I10">
         <v>1</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="J10" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>115</v>
       </c>
@@ -2499,11 +2498,11 @@
       <c r="I11">
         <v>1</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="J11" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>118</v>
       </c>
@@ -2531,11 +2530,11 @@
       <c r="I12">
         <v>1</v>
       </c>
-      <c r="J12" s="2" t="s">
+      <c r="J12" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>113</v>
       </c>
@@ -2548,10 +2547,10 @@
       <c r="D13" t="s">
         <v>56</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="3" t="s">
         <v>248</v>
       </c>
       <c r="H13" t="s">
@@ -2560,11 +2559,11 @@
       <c r="I13">
         <v>0.1</v>
       </c>
-      <c r="J13" s="2" t="s">
+      <c r="J13" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>114</v>
       </c>
@@ -2580,10 +2579,10 @@
       <c r="E14" t="s">
         <v>82</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="3" t="s">
         <v>248</v>
       </c>
       <c r="H14" t="s">
@@ -2592,11 +2591,11 @@
       <c r="I14">
         <v>0.1</v>
       </c>
-      <c r="J14" s="2" t="s">
+      <c r="J14" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>121</v>
       </c>
@@ -2621,15 +2620,15 @@
       <c r="I15">
         <v>0.05</v>
       </c>
-      <c r="J15" s="2" t="s">
+      <c r="J15" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F16" t="s">
         <v>235</v>
       </c>
-      <c r="J16" s="2" t="s">
+      <c r="J16" t="s">
         <v>206</v>
       </c>
     </row>
@@ -2661,7 +2660,7 @@
       <c r="I17">
         <v>1</v>
       </c>
-      <c r="J17" s="2" t="s">
+      <c r="J17" t="s">
         <v>206</v>
       </c>
     </row>
@@ -2693,7 +2692,7 @@
       <c r="I18">
         <v>1</v>
       </c>
-      <c r="J18" s="2" t="s">
+      <c r="J18" t="s">
         <v>206</v>
       </c>
     </row>
@@ -2725,7 +2724,7 @@
       <c r="I19">
         <v>1</v>
       </c>
-      <c r="J19" s="2" t="s">
+      <c r="J19" t="s">
         <v>206</v>
       </c>
     </row>
@@ -2742,10 +2741,10 @@
       <c r="D20" t="s">
         <v>56</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G20" s="3" t="s">
         <v>248</v>
       </c>
       <c r="H20" t="s">
@@ -2754,7 +2753,7 @@
       <c r="I20">
         <v>0.1</v>
       </c>
-      <c r="J20" s="2" t="s">
+      <c r="J20" t="s">
         <v>205</v>
       </c>
     </row>
@@ -2774,10 +2773,10 @@
       <c r="E21" t="s">
         <v>82</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="F21" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="G21" s="3" t="s">
         <v>248</v>
       </c>
       <c r="H21" t="s">
@@ -2786,7 +2785,7 @@
       <c r="I21">
         <v>0.1</v>
       </c>
-      <c r="J21" s="2" t="s">
+      <c r="J21" t="s">
         <v>205</v>
       </c>
     </row>
@@ -2815,7 +2814,7 @@
       <c r="I22">
         <v>0.05</v>
       </c>
-      <c r="J22" s="2" t="s">
+      <c r="J22" t="s">
         <v>206</v>
       </c>
     </row>
@@ -2823,7 +2822,6 @@
       <c r="F23" t="s">
         <v>236</v>
       </c>
-      <c r="J23" s="2"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
@@ -2853,7 +2851,7 @@
       <c r="I24">
         <v>1</v>
       </c>
-      <c r="J24" s="2" t="s">
+      <c r="J24" t="s">
         <v>206</v>
       </c>
     </row>
@@ -2885,7 +2883,7 @@
       <c r="I25">
         <v>1</v>
       </c>
-      <c r="J25" s="2" t="s">
+      <c r="J25" t="s">
         <v>206</v>
       </c>
     </row>
@@ -2917,7 +2915,7 @@
       <c r="I26">
         <v>1</v>
       </c>
-      <c r="J26" s="2" t="s">
+      <c r="J26" t="s">
         <v>206</v>
       </c>
     </row>
@@ -2934,10 +2932,10 @@
       <c r="D27" t="s">
         <v>56</v>
       </c>
-      <c r="F27" s="4" t="s">
+      <c r="F27" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="G27" s="4" t="s">
+      <c r="G27" s="3" t="s">
         <v>248</v>
       </c>
       <c r="H27" t="s">
@@ -2946,7 +2944,7 @@
       <c r="I27">
         <v>0.1</v>
       </c>
-      <c r="J27" s="2" t="s">
+      <c r="J27" t="s">
         <v>205</v>
       </c>
     </row>
@@ -2966,10 +2964,10 @@
       <c r="E28" t="s">
         <v>82</v>
       </c>
-      <c r="F28" s="4" t="s">
+      <c r="F28" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="G28" s="4" t="s">
+      <c r="G28" s="3" t="s">
         <v>251</v>
       </c>
       <c r="H28" t="s">
@@ -2978,7 +2976,7 @@
       <c r="I28">
         <v>0.1</v>
       </c>
-      <c r="J28" s="2" t="s">
+      <c r="J28" t="s">
         <v>205</v>
       </c>
     </row>
@@ -3007,7 +3005,7 @@
       <c r="I29">
         <v>0.05</v>
       </c>
-      <c r="J29" s="2" t="s">
+      <c r="J29" t="s">
         <v>206</v>
       </c>
     </row>
@@ -3018,7 +3016,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.85546875" customWidth="1"/>
@@ -3057,674 +3055,706 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" t="s">
         <v>137</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2">
         <v>1.5</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2">
         <v>2.8</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" t="s">
         <v>138</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" t="s">
         <v>139</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" t="s">
         <v>140</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I2" s="2">
+      <c r="H2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I2">
+        <v>0.1</v>
+      </c>
+      <c r="J2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B3">
+        <v>0.65</v>
+      </c>
+      <c r="C3">
+        <v>0.65</v>
+      </c>
+      <c r="D3" t="s">
+        <v>142</v>
+      </c>
+      <c r="E3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F3" t="s">
+        <v>143</v>
+      </c>
+      <c r="G3" t="s">
+        <v>144</v>
+      </c>
+      <c r="H3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3">
         <v>0.05</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J3" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="B3" s="2">
-        <v>0.65</v>
-      </c>
-      <c r="C3" s="2">
-        <v>0.65</v>
-      </c>
-      <c r="D3" s="2" t="s">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B4">
+        <v>23</v>
+      </c>
+      <c r="C4">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F4" t="s">
+        <v>146</v>
+      </c>
+      <c r="G4" t="s">
+        <v>147</v>
+      </c>
+      <c r="H4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4">
+        <v>0.5</v>
+      </c>
+      <c r="J4" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>148</v>
+      </c>
+      <c r="B5">
+        <v>8</v>
+      </c>
+      <c r="C5">
+        <v>12</v>
+      </c>
+      <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F5" t="s">
+        <v>149</v>
+      </c>
+      <c r="G5" t="s">
+        <v>150</v>
+      </c>
+      <c r="H5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5">
+        <v>0.5</v>
+      </c>
+      <c r="J5" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>151</v>
+      </c>
+      <c r="B6">
+        <v>34</v>
+      </c>
+      <c r="C6">
+        <v>36</v>
+      </c>
+      <c r="D6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" t="s">
+        <v>68</v>
+      </c>
+      <c r="F6" t="s">
+        <v>152</v>
+      </c>
+      <c r="G6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I6">
+        <v>0.5</v>
+      </c>
+      <c r="J6" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>154</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" t="s">
+        <v>68</v>
+      </c>
+      <c r="F7" t="s">
+        <v>155</v>
+      </c>
+      <c r="G7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H7" t="s">
+        <v>27</v>
+      </c>
+      <c r="I7">
+        <v>0.5</v>
+      </c>
+      <c r="J7" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>157</v>
+      </c>
+      <c r="B8">
+        <v>9</v>
+      </c>
+      <c r="C8">
+        <v>11</v>
+      </c>
+      <c r="D8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" t="s">
+        <v>64</v>
+      </c>
+      <c r="F8" t="s">
+        <v>158</v>
+      </c>
+      <c r="G8" t="s">
+        <v>159</v>
+      </c>
+      <c r="H8" t="s">
+        <v>27</v>
+      </c>
+      <c r="I8">
+        <v>0.5</v>
+      </c>
+      <c r="J8" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>160</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+      <c r="D9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" t="s">
+        <v>64</v>
+      </c>
+      <c r="F9" t="s">
+        <v>161</v>
+      </c>
+      <c r="G9" t="s">
+        <v>162</v>
+      </c>
+      <c r="H9" t="s">
+        <v>27</v>
+      </c>
+      <c r="I9">
+        <v>0.5</v>
+      </c>
+      <c r="J9" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>163</v>
+      </c>
+      <c r="B10">
+        <v>0.8</v>
+      </c>
+      <c r="C10">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" t="s">
+        <v>64</v>
+      </c>
+      <c r="F10" t="s">
+        <v>164</v>
+      </c>
+      <c r="G10" t="s">
+        <v>165</v>
+      </c>
+      <c r="H10" t="s">
+        <v>27</v>
+      </c>
+      <c r="I10">
+        <v>0.5</v>
+      </c>
+      <c r="J10" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>252</v>
+      </c>
+      <c r="B11">
+        <v>0.13</v>
+      </c>
+      <c r="C11">
+        <v>0.18</v>
+      </c>
+      <c r="D11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E11" t="s">
+        <v>253</v>
+      </c>
+      <c r="F11" t="s">
+        <v>254</v>
+      </c>
+      <c r="G11" t="s">
+        <v>255</v>
+      </c>
+      <c r="H11" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11">
+        <v>0.01</v>
+      </c>
+      <c r="J11" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>166</v>
+      </c>
+      <c r="B12">
+        <v>0.9</v>
+      </c>
+      <c r="C12">
+        <v>0.9</v>
+      </c>
+      <c r="D12" t="s">
         <v>142</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E12" t="s">
+        <v>57</v>
+      </c>
+      <c r="F12" t="s">
+        <v>167</v>
+      </c>
+      <c r="G12" t="s">
+        <v>168</v>
+      </c>
+      <c r="H12" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12">
+        <v>0.05</v>
+      </c>
+      <c r="J12" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>169</v>
+      </c>
+      <c r="B13">
+        <v>0.9</v>
+      </c>
+      <c r="C13">
+        <v>0.9</v>
+      </c>
+      <c r="D13" t="s">
+        <v>142</v>
+      </c>
+      <c r="E13" t="s">
+        <v>57</v>
+      </c>
+      <c r="F13" t="s">
+        <v>170</v>
+      </c>
+      <c r="G13" t="s">
+        <v>171</v>
+      </c>
+      <c r="H13" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13">
+        <v>0.05</v>
+      </c>
+      <c r="J13" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>172</v>
+      </c>
+      <c r="B14">
+        <v>0.5</v>
+      </c>
+      <c r="C14">
+        <v>0.6</v>
+      </c>
+      <c r="D14" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14" t="s">
+        <v>57</v>
+      </c>
+      <c r="F14" t="s">
+        <v>173</v>
+      </c>
+      <c r="G14" t="s">
+        <v>174</v>
+      </c>
+      <c r="H14" t="s">
+        <v>32</v>
+      </c>
+      <c r="I14">
+        <v>0.05</v>
+      </c>
+      <c r="J14" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>175</v>
+      </c>
+      <c r="B15">
+        <v>25</v>
+      </c>
+      <c r="C15">
+        <v>30</v>
+      </c>
+      <c r="D15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" t="s">
+        <v>176</v>
+      </c>
+      <c r="F15" t="s">
+        <v>177</v>
+      </c>
+      <c r="G15" t="s">
+        <v>178</v>
+      </c>
+      <c r="H15" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="J15" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>179</v>
+      </c>
+      <c r="B16">
+        <v>15</v>
+      </c>
+      <c r="C16">
+        <v>20</v>
+      </c>
+      <c r="D16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" t="s">
+        <v>180</v>
+      </c>
+      <c r="F16" t="s">
+        <v>181</v>
+      </c>
+      <c r="G16" t="s">
+        <v>182</v>
+      </c>
+      <c r="H16" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+      <c r="J16" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>183</v>
+      </c>
+      <c r="B17">
+        <v>30</v>
+      </c>
+      <c r="C17">
+        <v>40</v>
+      </c>
+      <c r="D17" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" t="s">
+        <v>180</v>
+      </c>
+      <c r="F17" t="s">
+        <v>184</v>
+      </c>
+      <c r="G17" t="s">
+        <v>185</v>
+      </c>
+      <c r="H17" t="s">
+        <v>32</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+      <c r="J17" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>186</v>
+      </c>
+      <c r="B18">
+        <v>40</v>
+      </c>
+      <c r="C18">
+        <v>50</v>
+      </c>
+      <c r="D18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" t="s">
+        <v>180</v>
+      </c>
+      <c r="F18" t="s">
+        <v>187</v>
+      </c>
+      <c r="G18" t="s">
+        <v>188</v>
+      </c>
+      <c r="H18" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="J18" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>189</v>
+      </c>
+      <c r="B19">
+        <v>50</v>
+      </c>
+      <c r="C19">
+        <v>60</v>
+      </c>
+      <c r="D19" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" t="s">
+        <v>180</v>
+      </c>
+      <c r="F19" t="s">
+        <v>190</v>
+      </c>
+      <c r="G19" t="s">
+        <v>191</v>
+      </c>
+      <c r="H19" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19">
+        <v>1</v>
+      </c>
+      <c r="J19" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>192</v>
+      </c>
+      <c r="B20">
+        <v>0.6</v>
+      </c>
+      <c r="C20">
+        <v>0.8</v>
+      </c>
+      <c r="D20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" t="s">
         <v>80</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I3" s="2">
+      <c r="F20" t="s">
+        <v>193</v>
+      </c>
+      <c r="G20" t="s">
+        <v>194</v>
+      </c>
+      <c r="H20" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20">
         <v>0.05</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J20" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="B4" s="2">
-        <v>23</v>
-      </c>
-      <c r="C4" s="2">
-        <v>27</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I4" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="J4" s="2" t="s">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>195</v>
+      </c>
+      <c r="B21">
+        <v>1.3</v>
+      </c>
+      <c r="C21">
+        <v>1.5</v>
+      </c>
+      <c r="D21" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21" t="s">
+        <v>80</v>
+      </c>
+      <c r="F21" t="s">
+        <v>196</v>
+      </c>
+      <c r="G21" t="s">
+        <v>197</v>
+      </c>
+      <c r="H21" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21">
+        <v>0.05</v>
+      </c>
+      <c r="J21" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="B5" s="2">
-        <v>8</v>
-      </c>
-      <c r="C5" s="2">
-        <v>12</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I5" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="J5" s="2" t="s">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>198</v>
+      </c>
+      <c r="B22">
+        <v>1.4</v>
+      </c>
+      <c r="C22">
+        <v>1.6</v>
+      </c>
+      <c r="D22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22" t="s">
+        <v>80</v>
+      </c>
+      <c r="F22" t="s">
+        <v>199</v>
+      </c>
+      <c r="G22" t="s">
+        <v>200</v>
+      </c>
+      <c r="H22" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22">
+        <v>0.05</v>
+      </c>
+      <c r="J22" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="B6" s="2">
-        <v>34</v>
-      </c>
-      <c r="C6" s="2">
-        <v>36</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I6" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="B7" s="2">
-        <v>3</v>
-      </c>
-      <c r="C7" s="2">
-        <v>6</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I7" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="B8" s="2">
-        <v>9</v>
-      </c>
-      <c r="C8" s="2">
-        <v>11</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I8" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="B9" s="2">
-        <v>1</v>
-      </c>
-      <c r="C9" s="2">
-        <v>3</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I9" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="B10" s="2">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>201</v>
+      </c>
+      <c r="B23">
+        <v>0.4</v>
+      </c>
+      <c r="C23">
         <v>0.8</v>
       </c>
-      <c r="C10" s="2">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I10" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="B11" s="2">
-        <v>0.9</v>
-      </c>
-      <c r="C11" s="2">
-        <v>0.9</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I11" s="2">
-        <v>0.01</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="B12" s="2">
-        <v>0.9</v>
-      </c>
-      <c r="C12" s="2">
-        <v>0.9</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I12" s="2">
-        <v>0.01</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="B13" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="C13" s="2">
-        <v>0.6</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I13" s="2">
-        <v>0.01</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="B14" s="2">
-        <v>25</v>
-      </c>
-      <c r="C14" s="2">
-        <v>30</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I14" s="2">
-        <v>1</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="B15" s="2">
-        <v>15</v>
-      </c>
-      <c r="C15" s="2">
-        <v>20</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I15" s="2">
-        <v>1</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="B16" s="2">
-        <v>30</v>
-      </c>
-      <c r="C16" s="2">
-        <v>40</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I16" s="2">
-        <v>1</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="B17" s="2">
-        <v>40</v>
-      </c>
-      <c r="C17" s="2">
-        <v>50</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I17" s="2">
-        <v>1</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B18" s="2">
-        <v>50</v>
-      </c>
-      <c r="C18" s="2">
-        <v>60</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I18" s="2">
-        <v>1</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="B19" s="2">
-        <v>0.6</v>
-      </c>
-      <c r="C19" s="2">
-        <v>0.8</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="D23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E23" t="s">
         <v>80</v>
       </c>
-      <c r="F19" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I19" s="2">
+      <c r="F23" t="s">
+        <v>202</v>
+      </c>
+      <c r="G23" t="s">
+        <v>203</v>
+      </c>
+      <c r="H23" t="s">
+        <v>32</v>
+      </c>
+      <c r="I23">
         <v>0.05</v>
       </c>
-      <c r="J19" s="2" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="B20" s="2">
-        <v>1.3</v>
-      </c>
-      <c r="C20" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="B21" s="2">
-        <v>1.4</v>
-      </c>
-      <c r="C21" s="2">
-        <v>1.6</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I21" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="B22" s="2">
-        <v>0.4</v>
-      </c>
-      <c r="C22" s="2">
-        <v>0.8</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I22" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="J22" s="2" t="s">
+      <c r="J23" t="s">
         <v>205</v>
       </c>
     </row>
